--- a/Back-end/Ecommerce/Database/urls.xlsx
+++ b/Back-end/Ecommerce/Database/urls.xlsx
@@ -1,80 +1,214 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project E-commerce Web\Back-end\Ecommerce\Database\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543F3901-8838-41AD-8377-50401C3AC9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB1A409-FB74-4B4D-BB15-01568F6573E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17172" yWindow="480" windowWidth="23256" windowHeight="13896" xr2:uid="{3AE7C4D3-9673-45F5-BF42-5AA2405909A8}"/>
+    <workbookView xWindow="17172" yWindow="480" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="urls" sheetId="1" r:id="rId1"/>
+    <sheet name="valid_category_names" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t xml:space="preserve">URL cửa hàng </t>
-  </si>
-  <si>
-    <t>category_id</t>
-  </si>
-  <si>
-    <t>http://lazada.vn/shop/dien-tu-ky-thuat-so-3c/?spm=a2o4n.pdp_revamp.seller.2.78a4458fSikO8g&amp;itemId=2929447409&amp;channelSource=pdp</t>
-  </si>
-  <si>
-    <t>https://www.lazada.vn/shop/bsnt-pn/?spm=a2o4n.pdp_revamp.seller.2.500228d9crH7BK&amp;itemId=2948802023&amp;channelSource=pdp</t>
-  </si>
-  <si>
-    <t>https://www.lazada.vn/shop/thelinhstore/?spm=a2o4n.pdp_revamp.seller.2.78062ffaRraScY&amp;itemId=3294028905&amp;channelSource=pdp</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+  <si>
+    <t>shop_url</t>
+  </si>
+  <si>
+    <t>category_name</t>
+  </si>
+  <si>
+    <t>category_name (con) hợp lệ — copy đúng tên vào cột category_name ở sheet 'urls'</t>
+  </si>
+  <si>
+    <t>── Điện thoại - Máy tính bảng ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Điện thoại smartphone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Máy tính bảng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Phụ kiện điện thoại</t>
+  </si>
+  <si>
+    <t>── Thời trang ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Thời trang nam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Thời trang nữ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Giày dép</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Túi ví</t>
+  </si>
+  <si>
+    <t>── Điện tử - Điện lạnh ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Tivi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Tủ lạnh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Máy giặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Máy lạnh</t>
+  </si>
+  <si>
+    <t>── Máy tính - Laptop ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Laptop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Linh kiện máy tính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Thiết bị mạng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Phần mềm bản quyền</t>
+  </si>
+  <si>
+    <t>── Đồ gia dụng ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Đồ dùng nhà bếp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Đồ dùng phòng tắm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Nội thất nhỏ</t>
+  </si>
+  <si>
+    <t>── Mẹ và Bé ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Sữa bột</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Đồ chơi trẻ em</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Quần áo trẻ em</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Tã - Bỉm</t>
+  </si>
+  <si>
+    <t>── Sách - Văn phòng phẩm ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Sách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Dụng cụ học tập</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Văn phòng phẩm</t>
+  </si>
+  <si>
+    <t>── Thể thao - Du lịch ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Dụng cụ thể thao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Balo - Vali du lịch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Xe đạp</t>
+  </si>
+  <si>
+    <t>── Làm đẹp - Sức khỏe ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Mỹ phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Chăm sóc da</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Thực phẩm chức năng</t>
+  </si>
+  <si>
+    <t>── Ô tô - Xe máy ──</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Phụ tùng xe máy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Phụ kiện ô tô</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Đồ chơi xe điều khiển</t>
+  </si>
+  <si>
+    <t>https://www.lazada.vn/shop/tuanviet-books/</t>
+  </si>
+  <si>
+    <t>Sách</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -89,8 +223,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -119,44 +258,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -184,31 +323,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -236,23 +358,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -264,136 +369,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -415,58 +564,277 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33975F66-E36E-44E7-B87B-BB1371E2F33D}">
-  <dimension ref="A1:B4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="24" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <f>B2+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <f>B3+1</f>
-        <v>3</v>
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42.140625" customWidth="1"/>
+    <col min="2" max="24" width="13.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>